--- a/Project_ETF/ETF_Investment_Portfolio/009805/ETF_Investment_Portfolio_20260810.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/009805/ETF_Investment_Portfolio_20260810.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D71"/>
+  <dimension ref="A1:D72"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24.75" customWidth="1" min="1" max="1"/>
@@ -616,7 +616,7 @@
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>11.40%</t>
+          <t>11.46%</t>
         </is>
       </c>
     </row>
@@ -638,7 +638,7 @@
       </c>
       <c r="D22" s="4" t="inlineStr">
         <is>
-          <t>10.43%</t>
+          <t>10.58%</t>
         </is>
       </c>
     </row>
@@ -660,7 +660,7 @@
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>7.99%</t>
+          <t>8.04%</t>
         </is>
       </c>
     </row>
@@ -682,7 +682,7 @@
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
-          <t>7.76%</t>
+          <t>7.74%</t>
         </is>
       </c>
     </row>
@@ -704,7 +704,7 @@
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>5.37%</t>
+          <t>5.45%</t>
         </is>
       </c>
     </row>
@@ -726,7 +726,7 @@
       </c>
       <c r="D26" s="4" t="inlineStr">
         <is>
-          <t>4.21%</t>
+          <t>4.15%</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,7 @@
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>3.50%</t>
+          <t>3.40%</t>
         </is>
       </c>
     </row>
@@ -792,7 +792,7 @@
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>3.24%</t>
+          <t>3.22%</t>
         </is>
       </c>
     </row>
@@ -836,7 +836,7 @@
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t>2.57%</t>
+          <t>2.59%</t>
         </is>
       </c>
     </row>
@@ -858,73 +858,73 @@
       </c>
       <c r="D32" s="4" t="inlineStr">
         <is>
-          <t>2.21%</t>
+          <t>2.19%</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="inlineStr">
         <is>
-          <t>EXC US</t>
+          <t>CEG US</t>
         </is>
       </c>
       <c r="B33" s="3" t="inlineStr">
         <is>
-          <t>Exelon Corp</t>
+          <t>星座能源公司</t>
         </is>
       </c>
       <c r="C33" s="4" t="inlineStr">
         <is>
-          <t>132,901</t>
+          <t>21,931</t>
         </is>
       </c>
       <c r="D33" s="4" t="inlineStr">
         <is>
-          <t>2.02%</t>
+          <t>2.00%</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="3" t="inlineStr">
         <is>
-          <t>FSLR US</t>
+          <t>EXC US</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
         <is>
-          <t>第一太陽能</t>
+          <t>Exelon Corp</t>
         </is>
       </c>
       <c r="C34" s="4" t="inlineStr">
         <is>
-          <t>23,704</t>
+          <t>132,901</t>
         </is>
       </c>
       <c r="D34" s="4" t="inlineStr">
         <is>
-          <t>1.98%</t>
+          <t>2.00%</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="3" t="inlineStr">
         <is>
-          <t>CEG US</t>
+          <t>FSLR US</t>
         </is>
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>星座能源公司</t>
+          <t>第一太陽能</t>
         </is>
       </c>
       <c r="C35" s="4" t="inlineStr">
         <is>
-          <t>21,931</t>
+          <t>23,704</t>
         </is>
       </c>
       <c r="D35" s="4" t="inlineStr">
         <is>
-          <t>1.97%</t>
+          <t>1.92%</t>
         </is>
       </c>
     </row>
@@ -1034,29 +1034,29 @@
       </c>
       <c r="D40" s="4" t="inlineStr">
         <is>
-          <t>1.18%</t>
+          <t>1.17%</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="3" t="inlineStr">
         <is>
-          <t>ACM UN</t>
+          <t>WEC US</t>
         </is>
       </c>
       <c r="B41" s="3" t="inlineStr">
         <is>
-          <t>艾奕康</t>
+          <t>WEC能源集團公司</t>
         </is>
       </c>
       <c r="C41" s="4" t="inlineStr">
         <is>
-          <t>45,827</t>
+          <t>31,710</t>
         </is>
       </c>
       <c r="D41" s="4" t="inlineStr">
         <is>
-          <t>1.16%</t>
+          <t>1.14%</t>
         </is>
       </c>
     </row>
@@ -1085,17 +1085,17 @@
     <row r="43">
       <c r="A43" s="3" t="inlineStr">
         <is>
-          <t>WEC US</t>
+          <t>ACM UN</t>
         </is>
       </c>
       <c r="B43" s="3" t="inlineStr">
         <is>
-          <t>WEC能源集團公司</t>
+          <t>艾奕康</t>
         </is>
       </c>
       <c r="C43" s="4" t="inlineStr">
         <is>
-          <t>31,710</t>
+          <t>45,827</t>
         </is>
       </c>
       <c r="D43" s="4" t="inlineStr">
@@ -1122,7 +1122,7 @@
       </c>
       <c r="D44" s="4" t="inlineStr">
         <is>
-          <t>1.09%</t>
+          <t>1.10%</t>
         </is>
       </c>
     </row>
@@ -1166,7 +1166,7 @@
       </c>
       <c r="D46" s="4" t="inlineStr">
         <is>
-          <t>1.02%</t>
+          <t>1.05%</t>
         </is>
       </c>
     </row>
@@ -1210,7 +1210,7 @@
       </c>
       <c r="D48" s="4" t="inlineStr">
         <is>
-          <t>0.98%</t>
+          <t>0.97%</t>
         </is>
       </c>
     </row>
@@ -1232,7 +1232,7 @@
       </c>
       <c r="D49" s="4" t="inlineStr">
         <is>
-          <t>0.96%</t>
+          <t>0.95%</t>
         </is>
       </c>
     </row>
@@ -1254,7 +1254,7 @@
       </c>
       <c r="D50" s="4" t="inlineStr">
         <is>
-          <t>0.95%</t>
+          <t>0.94%</t>
         </is>
       </c>
     </row>
@@ -1276,7 +1276,7 @@
       </c>
       <c r="D51" s="4" t="inlineStr">
         <is>
-          <t>0.94%</t>
+          <t>0.93%</t>
         </is>
       </c>
     </row>
@@ -1320,7 +1320,7 @@
       </c>
       <c r="D53" s="4" t="inlineStr">
         <is>
-          <t>0.83%</t>
+          <t>0.82%</t>
         </is>
       </c>
     </row>
@@ -1342,7 +1342,7 @@
       </c>
       <c r="D54" s="4" t="inlineStr">
         <is>
-          <t>0.83%</t>
+          <t>0.82%</t>
         </is>
       </c>
     </row>
@@ -1386,7 +1386,7 @@
       </c>
       <c r="D56" s="4" t="inlineStr">
         <is>
-          <t>0.78%</t>
+          <t>0.79%</t>
         </is>
       </c>
     </row>
@@ -1408,7 +1408,7 @@
       </c>
       <c r="D57" s="4" t="inlineStr">
         <is>
-          <t>0.73%</t>
+          <t>0.72%</t>
         </is>
       </c>
     </row>
@@ -1430,7 +1430,7 @@
       </c>
       <c r="D58" s="4" t="inlineStr">
         <is>
-          <t>0.71%</t>
+          <t>0.70%</t>
         </is>
       </c>
     </row>
@@ -1518,51 +1518,51 @@
       </c>
       <c r="D62" s="4" t="inlineStr">
         <is>
-          <t>0.52%</t>
+          <t>0.53%</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="3" t="inlineStr">
         <is>
-          <t>POWL US</t>
+          <t>AES US</t>
         </is>
       </c>
       <c r="B63" s="3" t="inlineStr">
         <is>
-          <t>Powell工業公司</t>
+          <t>愛伊斯公司</t>
         </is>
       </c>
       <c r="C63" s="4" t="inlineStr">
         <is>
-          <t>6,627</t>
+          <t>92,102</t>
         </is>
       </c>
       <c r="D63" s="4" t="inlineStr">
         <is>
-          <t>0.47%</t>
+          <t>0.46%</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="3" t="inlineStr">
         <is>
-          <t>AES US</t>
+          <t>POWL US</t>
         </is>
       </c>
       <c r="B64" s="3" t="inlineStr">
         <is>
-          <t>愛伊斯公司</t>
+          <t>Powell工業公司</t>
         </is>
       </c>
       <c r="C64" s="4" t="inlineStr">
         <is>
-          <t>92,102</t>
+          <t>6,627</t>
         </is>
       </c>
       <c r="D64" s="4" t="inlineStr">
         <is>
-          <t>0.45%</t>
+          <t>0.46%</t>
         </is>
       </c>
     </row>
@@ -1584,7 +1584,7 @@
       </c>
       <c r="D65" s="4" t="inlineStr">
         <is>
-          <t>0.43%</t>
+          <t>0.41%</t>
         </is>
       </c>
     </row>
@@ -1635,17 +1635,17 @@
     <row r="68">
       <c r="A68" s="3" t="inlineStr">
         <is>
-          <t>BELFB US</t>
+          <t>ITRI US</t>
         </is>
       </c>
       <c r="B68" s="3" t="inlineStr">
         <is>
-          <t>百富電子有限公司</t>
+          <t>英特隆公司</t>
         </is>
       </c>
       <c r="C68" s="4" t="inlineStr">
         <is>
-          <t>2,739</t>
+          <t>7,821</t>
         </is>
       </c>
       <c r="D68" s="4" t="inlineStr">
@@ -1657,22 +1657,22 @@
     <row r="69">
       <c r="A69" s="3" t="inlineStr">
         <is>
-          <t>ITRI US</t>
+          <t>BELFB US</t>
         </is>
       </c>
       <c r="B69" s="3" t="inlineStr">
         <is>
-          <t>英特隆公司</t>
+          <t>百富電子有限公司</t>
         </is>
       </c>
       <c r="C69" s="4" t="inlineStr">
         <is>
-          <t>7,821</t>
+          <t>2,739</t>
         </is>
       </c>
       <c r="D69" s="4" t="inlineStr">
         <is>
-          <t>0.27%</t>
+          <t>0.26%</t>
         </is>
       </c>
     </row>
@@ -1719,6 +1719,20 @@
           <t>0.01%</t>
         </is>
       </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="3" t="inlineStr">
+        <is>
+          <t>C_NTD</t>
+        </is>
+      </c>
+      <c r="B72" s="3" t="inlineStr"/>
+      <c r="C72" s="4" t="inlineStr">
+        <is>
+          <t>118,823,581</t>
+        </is>
+      </c>
+      <c r="D72" s="4" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="5">
